--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/69.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/69.xlsx
@@ -426,13 +426,13 @@
         <v>-4.134500422240182</v>
       </c>
       <c r="E2">
-        <v>-12.27286258953698</v>
+        <v>-14.19439149429348</v>
       </c>
       <c r="F2">
-        <v>-2.049539319947419</v>
+        <v>-2.800339227516182</v>
       </c>
       <c r="G2">
-        <v>-2.720422732589168</v>
+        <v>-2.50676722748623</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.491917712144448</v>
       </c>
       <c r="E3">
-        <v>-14.46149282101585</v>
+        <v>-15.10028994846508</v>
       </c>
       <c r="F3">
-        <v>-2.287247629854765</v>
+        <v>-2.659957460498556</v>
       </c>
       <c r="G3">
-        <v>-3.031354581156987</v>
+        <v>-3.156545005790051</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.083005672848868</v>
       </c>
       <c r="E4">
-        <v>-14.86444569017337</v>
+        <v>-14.57239186981142</v>
       </c>
       <c r="F4">
-        <v>-1.93808662773776</v>
+        <v>-2.804564729637862</v>
       </c>
       <c r="G4">
-        <v>-1.162056232430692</v>
+        <v>-2.324673013745261</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.976634541926641</v>
       </c>
       <c r="E5">
-        <v>-13.98478722515203</v>
+        <v>-14.87502391941771</v>
       </c>
       <c r="F5">
-        <v>-1.871594404682446</v>
+        <v>-2.655728644907264</v>
       </c>
       <c r="G5">
-        <v>-1.130053725232826</v>
+        <v>-2.33841336252829</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.124811902999997</v>
       </c>
       <c r="E6">
-        <v>-14.18641317533849</v>
+        <v>-15.87706506254776</v>
       </c>
       <c r="F6">
-        <v>-2.788215242208809</v>
+        <v>-2.695357741457192</v>
       </c>
       <c r="G6">
-        <v>-1.804161032381231</v>
+        <v>-1.708364981099512</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.49623512325418</v>
       </c>
       <c r="E7">
-        <v>-15.30758503210992</v>
+        <v>-16.48377032609004</v>
       </c>
       <c r="F7">
-        <v>-2.685735425706273</v>
+        <v>-2.989135755757828</v>
       </c>
       <c r="G7">
-        <v>-2.095572343641297</v>
+        <v>-2.01340960061437</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.021511206720041</v>
       </c>
       <c r="E8">
-        <v>-16.53997988816027</v>
+        <v>-17.38912055636677</v>
       </c>
       <c r="F8">
-        <v>-2.272817469697998</v>
+        <v>-2.519432385920244</v>
       </c>
       <c r="G8">
-        <v>-1.670592728355285</v>
+        <v>-1.224763706764642</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.648743078370481</v>
       </c>
       <c r="E9">
-        <v>-16.35270743631243</v>
+        <v>-17.0745314113563</v>
       </c>
       <c r="F9">
-        <v>-2.188118559496554</v>
+        <v>-2.453315413298399</v>
       </c>
       <c r="G9">
-        <v>-1.707010004656724</v>
+        <v>-1.195097815975822</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.303033629695957</v>
       </c>
       <c r="E10">
-        <v>-16.55088622109927</v>
+        <v>-17.48886407954385</v>
       </c>
       <c r="F10">
-        <v>-2.132559957790791</v>
+        <v>-2.209833382593541</v>
       </c>
       <c r="G10">
-        <v>-0.9670283899853475</v>
+        <v>-1.747343397844833</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.92488813653893</v>
       </c>
       <c r="E11">
-        <v>-18.01782953350799</v>
+        <v>-18.23225152778623</v>
       </c>
       <c r="F11">
-        <v>-1.88169137495517</v>
+        <v>-2.293612804977877</v>
       </c>
       <c r="G11">
-        <v>-0.5164190950483766</v>
+        <v>-1.386945771509191</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.461196303439189</v>
       </c>
       <c r="E12">
-        <v>-17.9641866560365</v>
+        <v>-19.04922142107061</v>
       </c>
       <c r="F12">
-        <v>-1.575072009176335</v>
+        <v>-1.978047899616211</v>
       </c>
       <c r="G12">
-        <v>-1.468442774665383</v>
+        <v>-1.122748861866891</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.86749680586043</v>
       </c>
       <c r="E13">
-        <v>-19.39720653834402</v>
+        <v>-19.90231594645834</v>
       </c>
       <c r="F13">
-        <v>-1.659975526126271</v>
+        <v>-1.865027107913052</v>
       </c>
       <c r="G13">
-        <v>-1.050768022745306</v>
+        <v>-1.513660870983465</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.131654791227281</v>
       </c>
       <c r="E14">
-        <v>-20.76524112305194</v>
+        <v>-19.77527336524316</v>
       </c>
       <c r="F14">
-        <v>-0.8569172325844984</v>
+        <v>-1.191631507196681</v>
       </c>
       <c r="G14">
-        <v>-1.447256582308499</v>
+        <v>-1.298561624121641</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.247938672799677</v>
       </c>
       <c r="E15">
-        <v>-21.5091767951892</v>
+        <v>-20.4016939229444</v>
       </c>
       <c r="F15">
-        <v>-0.8531581013105942</v>
+        <v>-1.200223333898517</v>
       </c>
       <c r="G15">
-        <v>-1.190421972413138</v>
+        <v>-1.351638061658974</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.238778077952651</v>
       </c>
       <c r="E16">
-        <v>-19.10438022067565</v>
+        <v>-20.49341759505323</v>
       </c>
       <c r="F16">
-        <v>-0.2745078506568191</v>
+        <v>-0.9144581174851604</v>
       </c>
       <c r="G16">
-        <v>-0.5953862866957801</v>
+        <v>-1.170368843208797</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.137943666134444</v>
       </c>
       <c r="E17">
-        <v>-21.33823892348191</v>
+        <v>-21.94374806216264</v>
       </c>
       <c r="F17">
-        <v>-0.4701193575212972</v>
+        <v>-0.5315626812565477</v>
       </c>
       <c r="G17">
-        <v>-0.3832554564340523</v>
+        <v>-0.8765060427776765</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.979298871114737</v>
       </c>
       <c r="E18">
-        <v>-22.71067591219415</v>
+        <v>-22.17766523039963</v>
       </c>
       <c r="F18">
-        <v>-0.1025263523245998</v>
+        <v>-0.4998237842182847</v>
       </c>
       <c r="G18">
-        <v>-0.7141986622927546</v>
+        <v>-1.58944295422971</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.806532058868237</v>
       </c>
       <c r="E19">
-        <v>-21.86641526729433</v>
+        <v>-22.71592972452006</v>
       </c>
       <c r="F19">
-        <v>0.2731664293366712</v>
+        <v>-0.3829933308296508</v>
       </c>
       <c r="G19">
-        <v>-0.6142436948773914</v>
+        <v>-2.260480025738967</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.639545804782321</v>
       </c>
       <c r="E20">
-        <v>-21.8458527180251</v>
+        <v>-23.59403073529458</v>
       </c>
       <c r="F20">
-        <v>0.283628709634029</v>
+        <v>0.288925290807529</v>
       </c>
       <c r="G20">
-        <v>-0.7117758913122015</v>
+        <v>-1.818290382108336</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.505377133512749</v>
       </c>
       <c r="E21">
-        <v>-24.23285693522308</v>
+        <v>-25.30269925323097</v>
       </c>
       <c r="F21">
-        <v>0.4587091304201213</v>
+        <v>0.2534711659677102</v>
       </c>
       <c r="G21">
-        <v>0.8947666787860877</v>
+        <v>-1.189829333390955</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.41895795186624</v>
       </c>
       <c r="E22">
-        <v>-24.59811941160778</v>
+        <v>-24.41121244235652</v>
       </c>
       <c r="F22">
-        <v>1.098026524552724</v>
+        <v>0.5694833897268879</v>
       </c>
       <c r="G22">
-        <v>-0.5191342694231343</v>
+        <v>-1.668814811288736</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.385047236292341</v>
       </c>
       <c r="E23">
-        <v>-25.91057987557817</v>
+        <v>-25.57352185730039</v>
       </c>
       <c r="F23">
-        <v>0.8930569511388197</v>
+        <v>0.9165295698645465</v>
       </c>
       <c r="G23">
-        <v>-1.603585357679771</v>
+        <v>-1.916655406067712</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.418907339144488</v>
       </c>
       <c r="E24">
-        <v>-24.70844947045185</v>
+        <v>-25.2279497558067</v>
       </c>
       <c r="F24">
-        <v>1.104181294355524</v>
+        <v>0.9848417161038104</v>
       </c>
       <c r="G24">
-        <v>-1.040985562762405</v>
+        <v>-1.502197091483886</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.508578714135375</v>
       </c>
       <c r="E25">
-        <v>-24.51367216574004</v>
+        <v>-25.88570629295377</v>
       </c>
       <c r="F25">
-        <v>1.567454048045176</v>
+        <v>1.413478771947609</v>
       </c>
       <c r="G25">
-        <v>-1.26666615745201</v>
+        <v>-2.001387121772293</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.658643589709331</v>
       </c>
       <c r="E26">
-        <v>-24.69533778229937</v>
+        <v>-25.77145975583039</v>
       </c>
       <c r="F26">
-        <v>1.520308345682245</v>
+        <v>2.078924530699314</v>
       </c>
       <c r="G26">
-        <v>-1.551349579900776</v>
+        <v>-2.015785378192283</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.856187906535506</v>
       </c>
       <c r="E27">
-        <v>-25.90164631801846</v>
+        <v>-26.81961400430002</v>
       </c>
       <c r="F27">
-        <v>1.935890331257923</v>
+        <v>1.294710767203827</v>
       </c>
       <c r="G27">
-        <v>-1.592035423608686</v>
+        <v>-2.426651308218736</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.085384259254186</v>
       </c>
       <c r="E28">
-        <v>-26.22654788674848</v>
+        <v>-26.78579440448194</v>
       </c>
       <c r="F28">
-        <v>1.960550828839264</v>
+        <v>1.772576041061195</v>
       </c>
       <c r="G28">
-        <v>-1.015637843527286</v>
+        <v>-2.395570393861533</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.34477993399633</v>
       </c>
       <c r="E29">
-        <v>-25.27962401111022</v>
+        <v>-26.10724273823145</v>
       </c>
       <c r="F29">
-        <v>1.525947870960503</v>
+        <v>1.80434227422375</v>
       </c>
       <c r="G29">
-        <v>-0.8327839031103023</v>
+        <v>-2.096063163624426</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.611966967035424</v>
       </c>
       <c r="E30">
-        <v>-25.55921819749768</v>
+        <v>-25.64348685527845</v>
       </c>
       <c r="F30">
-        <v>2.254883020932373</v>
+        <v>1.480526829530201</v>
       </c>
       <c r="G30">
-        <v>0.07062510147558353</v>
+        <v>-2.833063307972751</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.88857985661802</v>
       </c>
       <c r="E31">
-        <v>-26.12429997714252</v>
+        <v>-26.19480904580414</v>
       </c>
       <c r="F31">
-        <v>1.547601394869683</v>
+        <v>1.642078353893772</v>
       </c>
       <c r="G31">
-        <v>-1.152430417123257</v>
+        <v>-2.32148268385492</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.160932775078289</v>
       </c>
       <c r="E32">
-        <v>-25.10680058146146</v>
+        <v>-26.35415945791516</v>
       </c>
       <c r="F32">
-        <v>1.548883707609216</v>
+        <v>1.630201222072432</v>
       </c>
       <c r="G32">
-        <v>-1.682544717093401</v>
+        <v>-2.932684100080452</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.418536350644157</v>
       </c>
       <c r="E33">
-        <v>-25.14195751532613</v>
+        <v>-25.30836838668936</v>
       </c>
       <c r="F33">
-        <v>1.639139306348639</v>
+        <v>1.757456679225298</v>
       </c>
       <c r="G33">
-        <v>-1.293321859727277</v>
+        <v>-2.277094804316812</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.659538597169757</v>
       </c>
       <c r="E34">
-        <v>-24.40595447681929</v>
+        <v>-24.96535051016044</v>
       </c>
       <c r="F34">
-        <v>1.236575942875358</v>
+        <v>1.647537295078221</v>
       </c>
       <c r="G34">
-        <v>-1.016220039571104</v>
+        <v>-2.352769847034822</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.86373682965367</v>
       </c>
       <c r="E35">
-        <v>-22.76595930813894</v>
+        <v>-25.25059306394967</v>
       </c>
       <c r="F35">
-        <v>1.474620569948241</v>
+        <v>1.135712271175684</v>
       </c>
       <c r="G35">
-        <v>-1.303960643936064</v>
+        <v>-2.93338377963087</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.02991602857896</v>
       </c>
       <c r="E36">
-        <v>-24.44894436724259</v>
+        <v>-24.78621419929794</v>
       </c>
       <c r="F36">
-        <v>1.242727399208547</v>
+        <v>1.53509304708741</v>
       </c>
       <c r="G36">
-        <v>-1.407385290913016</v>
+        <v>-2.050187159669383</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.139411191301129</v>
       </c>
       <c r="E37">
-        <v>-23.4840661590471</v>
+        <v>-24.28888375599502</v>
       </c>
       <c r="F37">
-        <v>-0.1311646701741843</v>
+        <v>1.051831787968206</v>
       </c>
       <c r="G37">
-        <v>-0.5468394910240285</v>
+        <v>-2.335619865815799</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.179031127665503</v>
       </c>
       <c r="E38">
-        <v>-22.84583386833804</v>
+        <v>-23.3828980843856</v>
       </c>
       <c r="F38">
-        <v>0.6763701208123166</v>
+        <v>0.5947336848990225</v>
       </c>
       <c r="G38">
-        <v>0.3648325201927308</v>
+        <v>-2.098342343652468</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.141835848573464</v>
       </c>
       <c r="E39">
-        <v>-22.51200704847098</v>
+        <v>-22.64368046031334</v>
       </c>
       <c r="F39">
-        <v>1.682779357862923</v>
+        <v>0.4642906699801844</v>
       </c>
       <c r="G39">
-        <v>-0.3343066060952693</v>
+        <v>-1.940538497587216</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.010721208690423</v>
       </c>
       <c r="E40">
-        <v>-21.82894914793305</v>
+        <v>-21.97954043736001</v>
       </c>
       <c r="F40">
-        <v>1.153184196435532</v>
+        <v>0.6783076721674646</v>
       </c>
       <c r="G40">
-        <v>-0.4046531191028168</v>
+        <v>-1.74330196521779</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.793273149398908</v>
       </c>
       <c r="E41">
-        <v>-22.49765770334369</v>
+        <v>-22.02012561842623</v>
       </c>
       <c r="F41">
-        <v>0.11373635389167</v>
+        <v>0.5092105491317931</v>
       </c>
       <c r="G41">
-        <v>-0.4047914885661458</v>
+        <v>-1.509911841750626</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.487598841356286</v>
       </c>
       <c r="E42">
-        <v>-19.82518250573362</v>
+        <v>-22.36309780963057</v>
       </c>
       <c r="F42">
-        <v>0.1936406735657103</v>
+        <v>0.1121533437849201</v>
       </c>
       <c r="G42">
-        <v>-0.5711011405092443</v>
+        <v>-1.771518892758542</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.108176150873955</v>
       </c>
       <c r="E43">
-        <v>-21.97165764226548</v>
+        <v>-20.98335116898663</v>
       </c>
       <c r="F43">
-        <v>-0.402613212764957</v>
+        <v>-0.0708007091647815</v>
       </c>
       <c r="G43">
-        <v>0.2725139807063739</v>
+        <v>-1.35284683640466</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.678078585799773</v>
       </c>
       <c r="E44">
-        <v>-21.37432617668334</v>
+        <v>-21.01830044228507</v>
       </c>
       <c r="F44">
-        <v>0.718263145474096</v>
+        <v>-0.4250396034609481</v>
       </c>
       <c r="G44">
-        <v>0.9592625131649504</v>
+        <v>-1.141324309632662</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.212292906944453</v>
       </c>
       <c r="E45">
-        <v>-19.49953335896514</v>
+        <v>-20.82424164313245</v>
       </c>
       <c r="F45">
-        <v>0.1389328051826225</v>
+        <v>-0.2844060127528704</v>
       </c>
       <c r="G45">
-        <v>0.6593218993257183</v>
+        <v>-1.097727485705661</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.748759599800203</v>
       </c>
       <c r="E46">
-        <v>-20.26485806942527</v>
+        <v>-20.61532680707093</v>
       </c>
       <c r="F46">
-        <v>0.4357699803017974</v>
+        <v>-0.2303633233942307</v>
       </c>
       <c r="G46">
-        <v>0.1061573353606353</v>
+        <v>-0.8205943366143944</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.304705595448345</v>
       </c>
       <c r="E47">
-        <v>-18.88983778326899</v>
+        <v>-20.43016003336477</v>
       </c>
       <c r="F47">
-        <v>0.07796744943878732</v>
+        <v>-0.593143513980663</v>
       </c>
       <c r="G47">
-        <v>1.145142306563034</v>
+        <v>-1.004991227084726</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.908510721339359</v>
       </c>
       <c r="E48">
-        <v>-19.48928323341546</v>
+        <v>-20.35765327005592</v>
       </c>
       <c r="F48">
-        <v>0.1979680648779349</v>
+        <v>-0.3261391625059095</v>
       </c>
       <c r="G48">
-        <v>0.8209687614290885</v>
+        <v>-1.163419041107253</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.582901909235788</v>
       </c>
       <c r="E49">
-        <v>-19.20852199464573</v>
+        <v>-19.53469444604114</v>
       </c>
       <c r="F49">
-        <v>0.06786468059424454</v>
+        <v>-0.6251267794027519</v>
       </c>
       <c r="G49">
-        <v>-0.06838399427824338</v>
+        <v>-0.7062698309695435</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.334718386815331</v>
       </c>
       <c r="E50">
-        <v>-18.35801907312469</v>
+        <v>-19.23623637381631</v>
       </c>
       <c r="F50">
-        <v>-0.8557334955658978</v>
+        <v>-0.7325825988939038</v>
       </c>
       <c r="G50">
-        <v>-0.5632271348224467</v>
+        <v>-0.8770177487175347</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.186182314898515</v>
       </c>
       <c r="E51">
-        <v>-17.87364664915524</v>
+        <v>-18.51347377301303</v>
       </c>
       <c r="F51">
-        <v>0.07481799657334359</v>
+        <v>-0.7624253629471587</v>
       </c>
       <c r="G51">
-        <v>0.5033220777729261</v>
+        <v>-0.9825675417916537</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.129556009353842</v>
       </c>
       <c r="E52">
-        <v>-16.63532931375569</v>
+        <v>-18.41742660791504</v>
       </c>
       <c r="F52">
-        <v>-0.3524820742823366</v>
+        <v>-0.9684635303106741</v>
       </c>
       <c r="G52">
-        <v>1.048717065834856</v>
+        <v>-0.1520035327870108</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.168018752078273</v>
       </c>
       <c r="E53">
-        <v>-17.56020379047043</v>
+        <v>-17.76934705315482</v>
       </c>
       <c r="F53">
-        <v>-0.02054365883693549</v>
+        <v>-0.7718339599081555</v>
       </c>
       <c r="G53">
-        <v>0.7566086857689638</v>
+        <v>-0.8497093602944897</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.292203791582643</v>
       </c>
       <c r="E54">
-        <v>-17.65551999037524</v>
+        <v>-18.24401342225815</v>
       </c>
       <c r="F54">
-        <v>-0.2209257335741359</v>
+        <v>-1.041711089535818</v>
       </c>
       <c r="G54">
-        <v>0.2283297392463727</v>
+        <v>-1.079397447931454</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.482926634123592</v>
       </c>
       <c r="E55">
-        <v>-16.93451004475103</v>
+        <v>-17.94374454989569</v>
       </c>
       <c r="F55">
-        <v>-0.4862244765665252</v>
+        <v>-1.314938136940401</v>
       </c>
       <c r="G55">
-        <v>-0.06735536090934474</v>
+        <v>-0.5199723184368817</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.737368549973242</v>
       </c>
       <c r="E56">
-        <v>-16.27596024424092</v>
+        <v>-17.50441370274401</v>
       </c>
       <c r="F56">
-        <v>-0.4048638869983633</v>
+        <v>-1.625961103832517</v>
       </c>
       <c r="G56">
-        <v>0.3225201826045578</v>
+        <v>-0.895969143704426</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.029192506490332</v>
       </c>
       <c r="E57">
-        <v>-17.0328290164437</v>
+        <v>-17.11309397850734</v>
       </c>
       <c r="F57">
-        <v>-0.681485584019619</v>
+        <v>-1.561917534819879</v>
       </c>
       <c r="G57">
-        <v>-0.5448266069442802</v>
+        <v>-1.226366703943586</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.352789787717391</v>
       </c>
       <c r="E58">
-        <v>-16.63057388678876</v>
+        <v>-17.4283019520052</v>
       </c>
       <c r="F58">
-        <v>-0.4700158115959472</v>
+        <v>-1.129411174837604</v>
       </c>
       <c r="G58">
-        <v>0.07542887152323198</v>
+        <v>-0.8151770415878343</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.692725797900665</v>
       </c>
       <c r="E59">
-        <v>-16.11876950201881</v>
+        <v>-16.43673105462504</v>
       </c>
       <c r="F59">
-        <v>-1.329686390179843</v>
+        <v>-1.735405005090388</v>
       </c>
       <c r="G59">
-        <v>-0.5966864375021546</v>
+        <v>-0.7406428942561412</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.033182028132399</v>
       </c>
       <c r="E60">
-        <v>-15.32470456919087</v>
+        <v>-16.44149063480329</v>
       </c>
       <c r="F60">
-        <v>-1.315626510252127</v>
+        <v>-1.44703540156263</v>
       </c>
       <c r="G60">
-        <v>-1.026702179104424</v>
+        <v>-1.046468126403743</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.373270986381465</v>
       </c>
       <c r="E61">
-        <v>-15.48275502615722</v>
+        <v>-17.049288192924</v>
       </c>
       <c r="F61">
-        <v>-1.509423892504475</v>
+        <v>-1.595032350114192</v>
       </c>
       <c r="G61">
-        <v>-1.052619040660405</v>
+        <v>-1.695525339200416</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.692864718061328</v>
       </c>
       <c r="E62">
-        <v>-15.68390751025264</v>
+        <v>-15.55169002772672</v>
       </c>
       <c r="F62">
-        <v>-1.518733085377135</v>
+        <v>-2.023568345134849</v>
       </c>
       <c r="G62">
-        <v>-0.3902183122585514</v>
+        <v>-1.035589153692573</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.995113450985851</v>
       </c>
       <c r="E63">
-        <v>-13.97183751224122</v>
+        <v>-15.96559906835913</v>
       </c>
       <c r="F63">
-        <v>-1.585473818653289</v>
+        <v>-2.109672166451441</v>
       </c>
       <c r="G63">
-        <v>-1.119759559310066</v>
+        <v>-1.211999776458689</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.270680191533302</v>
       </c>
       <c r="E64">
-        <v>-14.23714880488259</v>
+        <v>-15.13229874814554</v>
       </c>
       <c r="F64">
-        <v>-1.292161346833026</v>
+        <v>-2.144534836965661</v>
       </c>
       <c r="G64">
-        <v>-1.875844246619429</v>
+        <v>-1.68387880757946</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.513045266349531</v>
       </c>
       <c r="E65">
-        <v>-15.92314078898541</v>
+        <v>-15.3603225095126</v>
       </c>
       <c r="F65">
-        <v>-1.373233664545013</v>
+        <v>-2.590238746409338</v>
       </c>
       <c r="G65">
-        <v>-1.245976006567438</v>
+        <v>-1.764308016197887</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.726856466085911</v>
       </c>
       <c r="E66">
-        <v>-14.04850994650888</v>
+        <v>-15.87217257960712</v>
       </c>
       <c r="F66">
-        <v>-1.819500863822594</v>
+        <v>-2.109393006636698</v>
       </c>
       <c r="G66">
-        <v>-1.02718516685378</v>
+        <v>-2.531932194599971</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.899251461851927</v>
       </c>
       <c r="E67">
-        <v>-14.44839774570867</v>
+        <v>-14.99074899977273</v>
       </c>
       <c r="F67">
-        <v>-2.471112058580144</v>
+        <v>-2.15101764025997</v>
       </c>
       <c r="G67">
-        <v>0.04242383840237782</v>
+        <v>-2.122371636869074</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.040679744766916</v>
       </c>
       <c r="E68">
-        <v>-15.11887556914369</v>
+        <v>-14.97633320326425</v>
       </c>
       <c r="F68">
-        <v>-1.679572213774299</v>
+        <v>-2.490477631722791</v>
       </c>
       <c r="G68">
-        <v>-1.972663709780865</v>
+        <v>-2.67490962213229</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.146452864708449</v>
       </c>
       <c r="E69">
-        <v>-12.20029352805825</v>
+        <v>-15.15556503798723</v>
       </c>
       <c r="F69">
-        <v>-2.380294826741623</v>
+        <v>-2.58242475669873</v>
       </c>
       <c r="G69">
-        <v>-1.21786350881033</v>
+        <v>-2.330474088226714</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.217887785663878</v>
       </c>
       <c r="E70">
-        <v>-14.6534334823928</v>
+        <v>-15.44711631977886</v>
       </c>
       <c r="F70">
-        <v>-2.016415392611675</v>
+        <v>-2.652764746340047</v>
       </c>
       <c r="G70">
-        <v>-2.03814901635976</v>
+        <v>-2.563506539684895</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.263473626353512</v>
       </c>
       <c r="E71">
-        <v>-13.34144233130212</v>
+        <v>-14.82528090738023</v>
       </c>
       <c r="F71">
-        <v>-2.398292765302247</v>
+        <v>-2.996673070755901</v>
       </c>
       <c r="G71">
-        <v>-0.9783485785324146</v>
+        <v>-2.431342816248967</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.27399933396053</v>
       </c>
       <c r="E72">
-        <v>-14.07915233966346</v>
+        <v>-14.81796294902589</v>
       </c>
       <c r="F72">
-        <v>-2.295965368401828</v>
+        <v>-2.712963862236293</v>
       </c>
       <c r="G72">
-        <v>-0.612254307498963</v>
+        <v>-2.621094343875672</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.262483954133092</v>
       </c>
       <c r="E73">
-        <v>-15.35947110119101</v>
+        <v>-14.76092689790202</v>
       </c>
       <c r="F73">
-        <v>-2.883611689050005</v>
+        <v>-2.87520375991159</v>
       </c>
       <c r="G73">
-        <v>-2.07836753678586</v>
+        <v>-2.410370704948554</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.221815017182797</v>
       </c>
       <c r="E74">
-        <v>-14.74609993347238</v>
+        <v>-15.50985473005172</v>
       </c>
       <c r="F74">
-        <v>-2.45406425743053</v>
+        <v>-2.916912887009948</v>
       </c>
       <c r="G74">
-        <v>-1.21652680757968</v>
+        <v>-3.361389247897982</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.153705405217732</v>
       </c>
       <c r="E75">
-        <v>-13.15175271046322</v>
+        <v>-15.29225552910998</v>
       </c>
       <c r="F75">
-        <v>-2.857625803624185</v>
+        <v>-3.099312762167177</v>
       </c>
       <c r="G75">
-        <v>-1.655638383337388</v>
+        <v>-2.017693832488387</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.06280177858932</v>
       </c>
       <c r="E76">
-        <v>-15.0029220621658</v>
+        <v>-15.44255194053288</v>
       </c>
       <c r="F76">
-        <v>-2.471243768997189</v>
+        <v>-3.115384746516293</v>
       </c>
       <c r="G76">
-        <v>-0.865410378265445</v>
+        <v>-2.224704992606942</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.93882998450573</v>
       </c>
       <c r="E77">
-        <v>-13.65795025994465</v>
+        <v>-16.55719910231301</v>
       </c>
       <c r="F77">
-        <v>-2.727132258293776</v>
+        <v>-2.986409598635215</v>
       </c>
       <c r="G77">
-        <v>-1.970734369528032</v>
+        <v>-2.004138846571327</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.796427346719186</v>
       </c>
       <c r="E78">
-        <v>-15.28727167552019</v>
+        <v>-16.53070576727193</v>
       </c>
       <c r="F78">
-        <v>-3.07009955734005</v>
+        <v>-3.326819727509047</v>
       </c>
       <c r="G78">
-        <v>-0.4966609799828312</v>
+        <v>-1.622823934571685</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.629243188828232</v>
       </c>
       <c r="E79">
-        <v>-16.24412172622479</v>
+        <v>-16.70721309536582</v>
       </c>
       <c r="F79">
-        <v>-2.838798669293357</v>
+        <v>-2.960621693018664</v>
       </c>
       <c r="G79">
-        <v>-0.4810957207306138</v>
+        <v>-2.239680223581567</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.444579552288383</v>
       </c>
       <c r="E80">
-        <v>-16.28584904040534</v>
+        <v>-17.789282467514</v>
       </c>
       <c r="F80">
-        <v>-2.952213763880249</v>
+        <v>-3.348843531647277</v>
       </c>
       <c r="G80">
-        <v>0.06466999306325412</v>
+        <v>-2.064546254920506</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.249206305905485</v>
       </c>
       <c r="E81">
-        <v>-19.08671661291116</v>
+        <v>-18.06920060438479</v>
       </c>
       <c r="F81">
-        <v>-2.837498960838365</v>
+        <v>-3.475759358164995</v>
       </c>
       <c r="G81">
-        <v>0.5372460929898522</v>
+        <v>-1.225131821751989</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.037214618125567</v>
       </c>
       <c r="E82">
-        <v>-19.6252012272318</v>
+        <v>-19.66546245781469</v>
       </c>
       <c r="F82">
-        <v>-3.200859008606757</v>
+        <v>-3.187102311148466</v>
       </c>
       <c r="G82">
-        <v>-0.09738675594092086</v>
+        <v>-1.605961135257684</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.826923406457959</v>
       </c>
       <c r="E83">
-        <v>-18.21646932475188</v>
+        <v>-20.66416441903959</v>
       </c>
       <c r="F83">
-        <v>-3.720966049802483</v>
+        <v>-3.185695743298512</v>
       </c>
       <c r="G83">
-        <v>1.164540138875006</v>
+        <v>-0.80069785208552</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.61441874873075</v>
       </c>
       <c r="E84">
-        <v>-20.00384950371642</v>
+        <v>-20.30044693726773</v>
       </c>
       <c r="F84">
-        <v>-3.143197182065286</v>
+        <v>-3.010541597813571</v>
       </c>
       <c r="G84">
-        <v>0.3137585237567816</v>
+        <v>-0.9376235736556385</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.415267441322448</v>
       </c>
       <c r="E85">
-        <v>-20.32586459057568</v>
+        <v>-22.07363559313533</v>
       </c>
       <c r="F85">
-        <v>-2.999655193405979</v>
+        <v>-3.431799556833231</v>
       </c>
       <c r="G85">
-        <v>0.8726458398655849</v>
+        <v>-0.937404271109985</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.241436643195629</v>
       </c>
       <c r="E86">
-        <v>-22.1304556772703</v>
+        <v>-23.48905001263689</v>
       </c>
       <c r="F86">
-        <v>-3.862169557283686</v>
+        <v>-3.233317756918053</v>
       </c>
       <c r="G86">
-        <v>0.628133944440279</v>
+        <v>-0.5151972665797355</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.096745481016631</v>
       </c>
       <c r="E87">
-        <v>-23.41916807888533</v>
+        <v>-25.08486747245503</v>
       </c>
       <c r="F87">
-        <v>-2.918727839989482</v>
+        <v>-2.854026547259021</v>
       </c>
       <c r="G87">
-        <v>0.1512370622153885</v>
+        <v>-0.2213422983823886</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.006198959884265</v>
       </c>
       <c r="E88">
-        <v>-24.78731064708769</v>
+        <v>-25.54518864964241</v>
       </c>
       <c r="F88">
-        <v>-2.973596411648713</v>
+        <v>-3.176811502903488</v>
       </c>
       <c r="G88">
-        <v>0.9775768864716101</v>
+        <v>-0.5954228371200557</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.967422866594909</v>
       </c>
       <c r="E89">
-        <v>-26.98096626426961</v>
+        <v>-27.58270013385606</v>
       </c>
       <c r="F89">
-        <v>-2.798306413909712</v>
+        <v>-3.094514858170162</v>
       </c>
       <c r="G89">
-        <v>1.224164323846851</v>
+        <v>-0.3114913091135303</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.999133025329162</v>
       </c>
       <c r="E90">
-        <v>-29.3034378839024</v>
+        <v>-28.35922813186492</v>
       </c>
       <c r="F90">
-        <v>-3.111015108466526</v>
+        <v>-3.131643113531039</v>
       </c>
       <c r="G90">
-        <v>0.7075423519235807</v>
+        <v>-0.3463891320629416</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.105913007972273</v>
       </c>
       <c r="E91">
-        <v>-31.35730886752456</v>
+        <v>-31.88234330696975</v>
       </c>
       <c r="F91">
-        <v>-2.980804864787874</v>
+        <v>-3.103434718363507</v>
       </c>
       <c r="G91">
-        <v>1.01221363496191</v>
+        <v>-0.8346531962375394</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.284412468798071</v>
       </c>
       <c r="E92">
-        <v>-31.58462035314942</v>
+        <v>-32.87889390472839</v>
       </c>
       <c r="F92">
-        <v>-2.666928172193113</v>
+        <v>-2.870674246953083</v>
       </c>
       <c r="G92">
-        <v>0.8164208443513692</v>
+        <v>-0.730915259909653</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.547505575829353</v>
       </c>
       <c r="E93">
-        <v>-32.27079316218096</v>
+        <v>-34.02188673380047</v>
       </c>
       <c r="F93">
-        <v>-2.928889422919623</v>
+        <v>-3.080066473930533</v>
       </c>
       <c r="G93">
-        <v>0.912587621365027</v>
+        <v>-1.166191651863016</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.876017067536636</v>
       </c>
       <c r="E94">
-        <v>-33.93779043428968</v>
+        <v>-35.87080712157066</v>
       </c>
       <c r="F94">
-        <v>-2.930227236275145</v>
+        <v>-3.04789848257762</v>
       </c>
       <c r="G94">
-        <v>0.9336406657477646</v>
+        <v>-0.9210349025237047</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.275839462011369</v>
       </c>
       <c r="E95">
-        <v>-37.50829167400514</v>
+        <v>-38.59532205708083</v>
       </c>
       <c r="F95">
-        <v>-2.70059136670808</v>
+        <v>-2.992291007195092</v>
       </c>
       <c r="G95">
-        <v>-0.6748860702397708</v>
+        <v>-1.843797356763513</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.736633156927773</v>
       </c>
       <c r="E96">
-        <v>-39.3629538764319</v>
+        <v>-39.24342860771466</v>
       </c>
       <c r="F96">
-        <v>-2.990740303417051</v>
+        <v>-2.998840079881625</v>
       </c>
       <c r="G96">
-        <v>0.08593711850246295</v>
+        <v>-1.899949251429178</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.237869162013766</v>
       </c>
       <c r="E97">
-        <v>-42.70545004423126</v>
+        <v>-42.31603456738703</v>
       </c>
       <c r="F97">
-        <v>-2.825086703674817</v>
+        <v>-2.865531742116503</v>
       </c>
       <c r="G97">
-        <v>0.01933963472775414</v>
+        <v>-2.040835472544015</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.788001969323885</v>
       </c>
       <c r="E98">
-        <v>-43.14347678302695</v>
+        <v>-43.90365774126128</v>
       </c>
       <c r="F98">
-        <v>-2.746856514521835</v>
+        <v>-2.63810678514751</v>
       </c>
       <c r="G98">
-        <v>-1.118036467879931</v>
+        <v>-2.729401083238006</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.34346606183044</v>
       </c>
       <c r="E99">
-        <v>-46.49694677344934</v>
+        <v>-45.62486688079299</v>
       </c>
       <c r="F99">
-        <v>-3.331209246376482</v>
+        <v>-2.753952309694216</v>
       </c>
       <c r="G99">
-        <v>-1.287990719272224</v>
+        <v>-2.283415416971897</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.92962592438746</v>
       </c>
       <c r="E100">
-        <v>-48.13763033690678</v>
+        <v>-48.06004627275332</v>
       </c>
       <c r="F100">
-        <v>-2.80952333691102</v>
+        <v>-2.664032199752926</v>
       </c>
       <c r="G100">
-        <v>-0.9948067124347928</v>
+        <v>-2.903848426071605</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.48855178243701</v>
       </c>
       <c r="E101">
-        <v>-50.12445291520374</v>
+        <v>-49.3511395027603</v>
       </c>
       <c r="F101">
-        <v>-2.371085866324701</v>
+        <v>-2.699013326805746</v>
       </c>
       <c r="G101">
-        <v>-1.960967574012678</v>
+        <v>-3.668337100219762</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.07168232752752</v>
       </c>
       <c r="E102">
-        <v>-51.82411207947374</v>
+        <v>-51.62282669261592</v>
       </c>
       <c r="F102">
-        <v>-2.752707273487808</v>
+        <v>-3.027132140156839</v>
       </c>
       <c r="G102">
-        <v>-2.704121243362257</v>
+        <v>-3.927140211536822</v>
       </c>
     </row>
   </sheetData>
